--- a/output/pdf_financials_xlsx/NEWD.xlsx
+++ b/output/pdf_financials_xlsx/NEWD.xlsx
@@ -1926,13 +1926,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.734898</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.707425</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.333083</v>
       </c>
     </row>
     <row r="93">
@@ -3127,7 +3127,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -3373,7 +3377,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>1.734898</v>
       </c>

--- a/output/pdf_financials_xlsx/NEWD.xlsx
+++ b/output/pdf_financials_xlsx/NEWD.xlsx
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.015086</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>8.7e-05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000151</v>
       </c>
     </row>
     <row r="13">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.301092</v>
+        <v>-2.316178</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-12.984272</v>
+        <v>-12.984359</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.977862</v>
+        <v>-0.978013</v>
       </c>
     </row>
     <row r="28">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.301092</v>
+        <v>-2.316178</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-12.984272</v>
+        <v>-12.984359</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.977862</v>
+        <v>-0.978013</v>
       </c>
     </row>
     <row r="30">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.80587</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.272673</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.025815</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.80587</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.272673</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.025815</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.880158</v>
+        <v>0.07428800000000001</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.4906</v>
+        <v>0.217927</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.031073</v>
+        <v>0.005258</v>
       </c>
     </row>
     <row r="49">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">

--- a/output/pdf_financials_xlsx/NEWD.xlsx
+++ b/output/pdf_financials_xlsx/NEWD.xlsx
@@ -2294,7 +2294,7 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.210853</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -3848,7 +3848,11 @@
           <t>Proceeds from sale of investments (note 5)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
